--- a/SCRUM_Template_with_Epic_Feature_UserStory_Task.xlsx
+++ b/SCRUM_Template_with_Epic_Feature_UserStory_Task.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_Amrita\19CSE314_SoftwareEngineering_2024_25\LAB_HowTo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9705E464-9445-4054-B19E-8B027820B682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A0E10A-867A-4185-A525-A6D4BF8F9030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Team" sheetId="2" r:id="rId2"/>
+    <sheet name="Team" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$O$2</definedName>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="218">
   <si>
     <t>Epic</t>
   </si>
@@ -972,7 +972,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -985,7 +985,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1334,64 +1333,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="19"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="18"/>
     </row>
     <row r="2" spans="2:15" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="L2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="15" t="s">
+      <c r="N2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="O2" s="15" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1545,22 +1546,17 @@
       <c r="N11" s="10"/>
       <c r="O11" s="11"/>
     </row>
-    <row r="12" spans="2:15" s="12" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="2:15" s="12" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="2:15" s="12" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="2:15" s="12" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="2:15" s="12" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="17" s="12" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="18" s="12" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="19" s="12" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="20" s="12" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="21" s="12" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="22" s="12" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="23" s="12" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="24" s="12" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="25" s="12" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="26" s="12" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="27" s="12" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="17" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="18" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="19" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="20" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="21" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="22" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="23" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="24" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="25" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="26" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="27" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:D1"/>
@@ -1601,17 +1597,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13" t="s">
+      <c r="E1" s="12"/>
+      <c r="F1" s="12" t="s">
         <v>216</v>
       </c>
     </row>
